--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8400" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="UITest" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="121">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -149,27 +149,9 @@
     <t>Visible</t>
   </si>
   <si>
-    <t>TC-UI-06</t>
-  </si>
-  <si>
-    <t>TS-UI-06</t>
-  </si>
-  <si>
-    <t>Validate Edit Note functionality</t>
-  </si>
-  <si>
     <t>Work</t>
   </si>
   <si>
-    <t>Original Title Block</t>
-  </si>
-  <si>
-    <t>Text description content block</t>
-  </si>
-  <si>
-    <t>Modified</t>
-  </si>
-  <si>
     <t>TC-UI-07</t>
   </si>
   <si>
@@ -269,27 +251,6 @@
     <t>Deleted via API layer while browser is open to check dynamic removal state</t>
   </si>
   <si>
-    <t>TC-E2E-03</t>
-  </si>
-  <si>
-    <t>TS-E2E-03</t>
-  </si>
-  <si>
-    <t>Validate multiple UI notes in API</t>
-  </si>
-  <si>
-    <t>Home|Work|Personal</t>
-  </si>
-  <si>
-    <t>Note One|Note Two|Note Three</t>
-  </si>
-  <si>
-    <t>Description Cluster A|Description Cluster B|Description Cluster C</t>
-  </si>
-  <si>
-    <t>Array Match</t>
-  </si>
-  <si>
     <t>TC-E2E-04</t>
   </si>
   <si>
@@ -411,13 +372,31 @@
   </si>
   <si>
     <t>Validate API response &lt; 2 seconds</t>
+  </si>
+  <si>
+    <t>TC-E2E-06</t>
+  </si>
+  <si>
+    <t>TS-E2E-06</t>
+  </si>
+  <si>
+    <t>Validate API -&gt; UI update sync</t>
+  </si>
+  <si>
+    <t>API Updated Sync Card</t>
+  </si>
+  <si>
+    <t>Modified via API PUT layer to test real-time text updates on dashboard fields.</t>
+  </si>
+  <si>
+    <t>Updated</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -436,6 +415,12 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Google Sans Text"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -474,12 +459,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -762,7 +750,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.5546875" customWidth="1"/>
@@ -917,7 +905,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="111" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>33</v>
       </c>
@@ -948,13 +936,13 @@
     </row>
     <row r="7" spans="1:9" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>12</v>
@@ -963,7 +951,7 @@
         <v>13</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>44</v>
@@ -975,7 +963,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="111" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>47</v>
       </c>
@@ -992,7 +980,7 @@
         <v>13</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>50</v>
@@ -1002,35 +990,6 @@
       </c>
       <c r="I8" s="2" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="97.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1085,13 +1044,13 @@
     </row>
     <row r="2" spans="1:9" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>12</v>
@@ -1114,13 +1073,13 @@
     </row>
     <row r="3" spans="1:9" ht="180" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>12</v>
@@ -1132,10 +1091,10 @@
         <v>25</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="I3" s="2">
         <v>201</v>
@@ -1143,13 +1102,13 @@
     </row>
     <row r="4" spans="1:9" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>12</v>
@@ -1172,13 +1131,13 @@
     </row>
     <row r="5" spans="1:9" ht="152.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>12</v>
@@ -1187,13 +1146,13 @@
         <v>13</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="I5" s="2">
         <v>200</v>
@@ -1201,13 +1160,13 @@
     </row>
     <row r="6" spans="1:9" ht="138.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>12</v>
@@ -1219,24 +1178,24 @@
         <v>36</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="I6" s="2">
         <v>204</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>12</v>
@@ -1309,13 +1268,13 @@
     </row>
     <row r="2" spans="1:9" ht="180" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>12</v>
@@ -1327,24 +1286,24 @@
         <v>25</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="193.8" thickBot="1" x14ac:dyDescent="0.35">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="83.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>12</v>
@@ -1356,71 +1315,71 @@
         <v>36</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="97.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="138.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="207.6" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:9" ht="83.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>92</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -1475,13 +1434,13 @@
     </row>
     <row r="2" spans="1:9" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>14</v>
@@ -1504,13 +1463,13 @@
     </row>
     <row r="3" spans="1:9" ht="97.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>12</v>
@@ -1533,16 +1492,16 @@
     </row>
     <row r="4" spans="1:9" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>20</v>
@@ -1562,13 +1521,13 @@
     </row>
     <row r="5" spans="1:9" ht="276.60000000000002" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>12</v>
@@ -1577,13 +1536,13 @@
         <v>13</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="I5" s="2">
         <v>400</v>
@@ -1591,19 +1550,19 @@
     </row>
     <row r="6" spans="1:9" ht="111" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>14</v>
@@ -1615,7 +1574,7 @@
         <v>14</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="127">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -372,6 +372,24 @@
   </si>
   <si>
     <t>Validate API response &lt; 2 seconds</t>
+  </si>
+  <si>
+    <t>TC-E2E-05</t>
+  </si>
+  <si>
+    <t>TS-E2E-05</t>
+  </si>
+  <si>
+    <t>Validate API -&gt; UI creation sync</t>
+  </si>
+  <si>
+    <t>API Created Sync Card</t>
+  </si>
+  <si>
+    <t>Injected via API POST layer to test real-time dynamic rendering on UI grid.</t>
+  </si>
+  <si>
+    <t>Present</t>
   </si>
   <si>
     <t>TC-E2E-06</t>
@@ -1223,7 +1241,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.6640625" customWidth="1"/>
@@ -1370,7 +1388,7 @@
         <v>13</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>118</v>
@@ -1380,6 +1398,35 @@
       </c>
       <c r="I5" s="2" t="s">
         <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="83.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>
